--- a/data/Data_Login.xlsx
+++ b/data/Data_Login.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t xml:space="preserve">email </t>
   </si>
@@ -35,33 +35,51 @@
     <t>password</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>expected</t>
   </si>
   <si>
+    <t>empty_all</t>
+  </si>
+  <si>
     <t>Please fill out this field.</t>
   </si>
   <si>
     <t>ddd28</t>
   </si>
   <si>
+    <t>email_empty</t>
+  </si>
+  <si>
     <t>lethithom2004</t>
   </si>
   <si>
     <t>dgc127</t>
   </si>
   <si>
+    <t>email_invalid</t>
+  </si>
+  <si>
     <t>Please include an '@' in the email address. 'lethithom2004' is missing an '@'.</t>
   </si>
   <si>
     <t>lethithom2004@gmail.com</t>
   </si>
   <si>
+    <t>password_empty</t>
+  </si>
+  <si>
     <t>lethithom@gmail.com</t>
   </si>
   <si>
     <t>thomne</t>
   </si>
   <si>
+    <t>login_fail</t>
+  </si>
+  <si>
     <t>Thông tin đăng nhập không hợp lệ.</t>
   </si>
   <si>
@@ -69,6 +87,9 @@
   </si>
   <si>
     <t>Thom12;hi</t>
+  </si>
+  <si>
+    <t>login_success</t>
   </si>
   <si>
     <t xml:space="preserve">TÀI KHOẢN CỦA BẠN </t>
@@ -84,13 +105,23 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -572,147 +603,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -728,7 +768,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1248,16 +1288,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="25.7142857142857" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="72.8571428571429" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.14285714285714" style="1"/>
+    <col min="1" max="1" width="30" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4285714285714" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1428571428571" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76.4285714285714" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.14285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1267,64 +1308,91 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
+    <row r="2" ht="16.5" spans="1:4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2"/>
+    <row r="3" ht="16.5" spans="1:4">
+      <c r="A3" s="3"/>
       <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
+    <row r="6" ht="16.5" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
+    <row r="7" ht="16.5" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
+    <row r="8" spans="1:4">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
